--- a/scripts/checks/results/HLR_results_11_Dunn_lgs_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_11_Dunn_lgs_Famfirst_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3059604222665624</v>
+        <v>0.2773093265883012</v>
       </c>
       <c r="H2" t="n">
-        <v>45.84736222052121</v>
+        <v>45.27870877721755</v>
       </c>
       <c r="I2" t="n">
-        <v>7.810452239193904e-10</v>
+        <v>6.498545364230793e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>14.92839846445508</v>
+        <v>17.9167062783317</v>
       </c>
       <c r="K2" t="n">
-        <v>21.50943396226416</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>6.581035497809081</v>
+        <v>6.874960388334969</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1435422929274527</v>
+        <v>0.151836493884167</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2048517520215634</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.8769068789051704, 'N1ratio-ArgsPreds': -0.25892073248774317}</t>
+          <t>{'const': 0.7704480129557647, 'N1ratio-ArgsPreds': -3.197547552292713}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.7265771913199485e-15, 'N1ratio-ArgsPreds': 7.810452239194086e-10}</t>
+          <t>{'const': 1.1179374076442262e-16, 'N1ratio-ArgsPreds': 6.498545364231103e-10}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5531368928814658}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5266016773504437}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5531368928814663)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504444)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5531368928814662)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504445)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.596042226656255)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(27.730932658830167)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3476503175884775</v>
+        <v>0.3409001611077889</v>
       </c>
       <c r="H3" t="n">
-        <v>27.44538985536318</v>
+        <v>30.25741814521527</v>
       </c>
       <c r="I3" t="n">
-        <v>2.790894677522507e-10</v>
+        <v>2.56239171087869e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>14.03167241413464</v>
+        <v>16.3401835058694</v>
       </c>
       <c r="K3" t="n">
-        <v>21.50943396226416</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>3.738880774064759</v>
+        <v>4.225741580398633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1362298292634431</v>
+        <v>0.1396596880843539</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2048517520215634</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.9611211826011918, 'N1ratio-ArgsPreds': -0.24402541624977742, 'Fam_class': -0.002986968938184703}</t>
+          <t>{'const': 0.8799286099669941, 'N1ratio-ArgsPreds': -2.9673419173463604, 'Fam_class': -0.0032709757323482725}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 2.3183274008404673e-16, 'N1ratio-ArgsPreds': 3.3230185967641215e-09, 'Fam_class': 0.011738588428515356}</t>
+          <t>{'const': 7.958996084822624e-19, 'N1ratio-ArgsPreds': 2.769771222493802e-09, 'Fam_class': 0.0010536502492942584}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5213157680793211, 'Fam_class': -0.20664578221098165}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48868928620825386, 'Fam_class': -0.25500624290711527}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5377063438432251), 'Fam_class': np.float64(-0.24508869754796073)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5114951182194193), 'Fam_class': np.float64(-0.29663407450257134)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5150978272666621), 'Fam_class': np.float64(-0.20418103565687704)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48325823941642665), 'Fam_class': np.float64(-0.25217223185649845)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(26.532577165483605), 'Fam_class': np.float64(4.168989532191489)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.353852596386435), 'Fam_class': np.float64(6.359083451948762)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.04168989532191514</v>
+        <v>0.06359083451948766</v>
       </c>
       <c r="V3" t="n">
-        <v>6.582450078435745</v>
+        <v>11.28831657929871</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01173858842851501</v>
+        <v>0.001053650249293891</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.454998915273213</v>
+        <v>0.4438874979987454</v>
       </c>
       <c r="H4" t="n">
-        <v>16.69717466714061</v>
+        <v>30.86362896150001</v>
       </c>
       <c r="I4" t="n">
-        <v>5.794027875875511e-12</v>
+        <v>9.65099385607767e-15</v>
       </c>
       <c r="J4" t="n">
-        <v>11.72266484129316</v>
+        <v>13.78695577878111</v>
       </c>
       <c r="K4" t="n">
-        <v>21.50943396226416</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9573538241942</v>
+        <v>3.668236962628522</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1172266484129316</v>
+        <v>0.1188530670584578</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2048517520215634</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.6390956805391634, 'N1ratio-ArgsPreds': -0.22578922616158775, 'Fam_class': -0.002279536807291536, 'latitude': -0.0005251232489778581, 'longitude': -0.0010411331253083072, 'Macro_class': 0.11757684971827559}</t>
+          <t>{'const': 0.39245795329586763, 'N1ratio-ArgsPreds': -2.8633566408845468, 'Fam_class': -0.0002931873723601736, 'Macro_class': 0.12862378502348515}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 0.0002704792054074353, 'N1ratio-ArgsPreds': 7.84110964511646e-09, 'Fam_class': 0.2266650031215392, 'latitude': 0.721823243349997, 'longitude': 0.09398637531539794, 'Macro_class': 0.00024134675563300105}</t>
+          <t>{'const': 0.0031357338238361095, 'N1ratio-ArgsPreds': 6.948974056809408e-10, 'Fam_class': 0.7910905256429878, 'Macro_class': 9.42111246867944e-06}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48235747599332707, 'Fam_class': -0.15770390532007428, 'latitude': -0.029244787087565057, 'longitude': -0.20212272850631371, 'Macro_class': 0.34554078046063097}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4715640300208119, 'Fam_class': -0.022856974924635984, 'Macro_class': 0.3979397223171519}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.533379062963635), 'Fam_class': np.float64(-0.12075793785607132), 'latitude': np.float64(-0.03568005552057562), 'longitude': np.float64(-0.16671544191103457), 'Macro_class': np.float64(0.3559176792527942)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5296671694897966), 'Fam_class': np.float64(-0.02464417907642201), 'Macro_class': np.float64(0.39529044010156983)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4655086679942658), 'Fam_class': np.float64(-0.08980576808409556), 'latitude': np.float64(-0.026357294175480963), 'longitude': np.float64(-0.12482321704586834), 'Macro_class': np.float64(0.2811647640366479)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4656753652021862), 'Fam_class': np.float64(-0.018383474902530714), 'Macro_class': np.float64(0.32091640171694724)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.66983199777956), 'Fam_class': np.float64(0.8065075981174357), 'latitude': np.float64(0.06947069562528427), 'longitude': np.float64(1.5580835513679956), 'Macro_class': np.float64(7.905362453578391)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.685354575618952), 'Fam_class': np.float64(0.03379521494919766), 'Macro_class': np.float64(10.298733689095306)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.1073485976847355</v>
+        <v>0.1029873368909565</v>
       </c>
       <c r="V4" t="n">
-        <v>6.565650399182241</v>
+        <v>21.48221993995741</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004259780885458649</v>
+        <v>9.42111246867966e-06</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4890634649576789</v>
+        <v>0.4619214611791158</v>
       </c>
       <c r="H5" t="n">
-        <v>13.40066336974782</v>
+        <v>19.57299642160542</v>
       </c>
       <c r="I5" t="n">
-        <v>4.989964903313688e-12</v>
+        <v>4.924562337235453e-14</v>
       </c>
       <c r="J5" t="n">
-        <v>10.98995565940087</v>
+        <v>13.33986377493442</v>
       </c>
       <c r="K5" t="n">
-        <v>21.50943396226416</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>1.502782614694755</v>
+        <v>2.29036057834645</v>
       </c>
       <c r="M5" t="n">
-        <v>0.112142404687764</v>
+        <v>0.1170163489029335</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2048517520215634</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.07174266864898833, 'N1ratio-ArgsPreds': -0.2210596848977188, 'Fam_class': -0.0047730797442658394, 'latitude': 0.0002667620768122361, 'longitude': -0.001357486184478533, 'Macro_class': 0.10147993435936409, 'Nlen_freq': 0.06963180770116842, 'Vlen_freq': 0.038537127158262525}</t>
+          <t>{'const': 0.17547142028804047, 'N1ratio-ArgsPreds': -2.985367830583771, 'Fam_class': -0.0013547988832419814, 'Macro_class': 0.1203900883589205, 'Nlen_freq': 0.7918523166300431, 'Vlen_freq': -0.05430434078500129}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.7972316822536216, 'N1ratio-ArgsPreds': 1.2220126715507511e-08, 'Fam_class': 0.025601998533387613, 'latitude': 0.8567082391104174, 'longitude': 0.02970201790040607, 'Macro_class': 0.0013936046111224162, 'Nlen_freq': 0.23396876351533372, 'Vlen_freq': 0.39836914689422387}</t>
+          <t>{'const': 0.318716671773403, 'N1ratio-ArgsPreds': 3.8674299916032e-10, 'Fam_class': 0.27046341802126433, 'Macro_class': 3.3361604837274294e-05, 'Nlen_freq': 0.13000228580547196, 'Vlen_freq': 0.9136473251109498}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47225367420690584, 'Fam_class': -0.33021327563876235, 'latitude': 0.01485632211979909, 'longitude': -0.2635386434709542, 'Macro_class': 0.2982343531371028, 'Nlen_freq': 0.1413234096002581, 'Vlen_freq': 0.0917262823217992}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4916579601658273, 'Fam_class': -0.10562052469348877, 'Macro_class': 0.3724660903311062, 'Nlen_freq': 0.16159289070001537, 'Vlen_freq': -0.01067839295176563}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5320484327272674), 'Fam_class': np.float64(-0.22320178764535017), 'latitude': np.float64(0.01828498028852819), 'longitude': np.float64(-0.21752858914001053), 'Macro_class': np.float64(0.31536518157283533), 'Nlen_freq': np.float64(0.12009834319410313), 'Vlen_freq': np.float64(0.08537275883879944)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.540257725193458), 'Fam_class': np.float64(-0.10316169926315122), 'Macro_class': np.float64(0.37514083559807176), 'Nlen_freq': np.float64(0.14140397636960284), 'Vlen_freq': np.float64(-0.010178292349248894)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4491567667618416), 'Fam_class': np.float64(-0.16367335530192872), 'latitude': np.float64(0.013072257346295116), 'longitude': np.float64(-0.15930374995601354), 'Macro_class': np.float64(0.2375442705402718), 'Nlen_freq': np.float64(0.08647196942162755), 'Vlen_freq': np.float64(0.06124790955774896)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4709446882582684), 'Fam_class': np.float64(-0.07607897649656697), 'Macro_class': np.float64(0.2968605689357376), 'Nlen_freq': np.float64(0.10477805456960126), 'Vlen_freq': np.float64(-0.007466554737971187)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.174180112795135), 'Fam_class': np.float64(2.67889672357914), 'latitude': np.float64(0.017088391212776662), 'longitude': np.float64(2.537768475004808), 'Macro_class': np.float64(5.642728046650984), 'Nlen_freq': np.float64(0.747740149565489), 'Vlen_freq': np.float64(0.37513064251941963)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.17888993986776), 'Fam_class': np.float64(0.5788010664765191), 'Macro_class': np.float64(8.81261973888498), 'Nlen_freq': np.float64(1.0978440719390339), 'Vlen_freq': np.float64(0.005574943965511998)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.03406454968446593</v>
+        <v>0.01803396318037043</v>
       </c>
       <c r="V5" t="n">
-        <v>3.266869405611351</v>
+        <v>1.910382643273</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04231652517548149</v>
+        <v>0.1527325792761614</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_11_Dunn_lgs_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_11_Dunn_lgs_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2773093265883012</v>
+        <v>0.2778077214292567</v>
       </c>
       <c r="H2" t="n">
-        <v>45.27870877721755</v>
+        <v>45.39138966360625</v>
       </c>
       <c r="I2" t="n">
-        <v>6.498545364230793e-10</v>
+        <v>6.23405371411057e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>17.9167062783317</v>
+        <v>17.90435023956635</v>
       </c>
       <c r="K2" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>6.874960388334969</v>
+        <v>6.887316427100323</v>
       </c>
       <c r="M2" t="n">
-        <v>0.151836493884167</v>
+        <v>0.1517317816912402</v>
       </c>
       <c r="N2" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7704480129557647, 'N1ratio-ArgsPreds': -3.197547552292713}</t>
+          <t>{'const': 0.7491199802103012, 'N1ratio-ArgsPreds': -3.0224806007943616}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 1.1179374076442262e-16, 'N1ratio-ArgsPreds': 6.498545364231103e-10}</t>
+          <t>{'const': 6.899475278910947e-17, 'N1ratio-ArgsPreds': 6.234053714110714e-10}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5266016773504437}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5270746829712618}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504444)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504445)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.730932658830167)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(27.78077214292572)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3409001611077889</v>
+        <v>0.3468783875246924</v>
       </c>
       <c r="H3" t="n">
-        <v>30.25741814521527</v>
+        <v>31.06984255701949</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56239171087869e-11</v>
+        <v>1.503668952114882e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>16.3401835058694</v>
+        <v>16.19197330928367</v>
       </c>
       <c r="K3" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>4.225741580398633</v>
+        <v>4.2998466786915</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1396596880843539</v>
+        <v>0.1383929342673818</v>
       </c>
       <c r="N3" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.8799286099669941, 'N1ratio-ArgsPreds': -2.9673419173463604, 'Fam_class': -0.0032709757323482725}</t>
+          <t>{'const': 0.8694669476332118, 'N1ratio-ArgsPreds': -2.8294009162073523, 'Fam_class': -0.0033986661667828}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 7.958996084822624e-19, 'N1ratio-ArgsPreds': 2.769771222493802e-09, 'Fam_class': 0.0010536502492942584}</t>
+          <t>{'const': 3.437321412929333e-19, 'N1ratio-ArgsPreds': 1.606111944602189e-09, 'Fam_class': 0.0006209671097238488}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48868928620825386, 'Fam_class': -0.25500624290711527}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49340452028596854, 'Fam_class': -0.2649610272298194}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5114951182194193), 'Fam_class': np.float64(-0.29663407450257134)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5180004928438996), 'Fam_class': np.float64(-0.30925761460178797)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48325823941642665), 'Fam_class': np.float64(-0.25217223185649845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48940448749553883), 'Fam_class': np.float64(-0.2628129869230889)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.353852596386435), 'Fam_class': np.float64(6.359083451948762)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.9516752380771), 'Fam_class': np.float64(6.907066609543571)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.06359083451948766</v>
+        <v>0.06907066609543566</v>
       </c>
       <c r="V3" t="n">
-        <v>11.28831657929871</v>
+        <v>12.37329737495327</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001053650249293891</v>
+        <v>0.0006209671097233587</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4438874979987454</v>
+        <v>0.4524291368054832</v>
       </c>
       <c r="H4" t="n">
-        <v>30.86362896150001</v>
+        <v>31.94824231714258</v>
       </c>
       <c r="I4" t="n">
-        <v>9.65099385607767e-15</v>
+        <v>3.96884339424559e-15</v>
       </c>
       <c r="J4" t="n">
-        <v>13.78695577878111</v>
+        <v>13.5751943166974</v>
       </c>
       <c r="K4" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L4" t="n">
-        <v>3.668236962628522</v>
+        <v>3.738824116656425</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1188530670584578</v>
+        <v>0.1170275372129086</v>
       </c>
       <c r="N4" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.39245795329586763, 'N1ratio-ArgsPreds': -2.8633566408845468, 'Fam_class': -0.0002931873723601736, 'Macro_class': 0.12862378502348515}</t>
+          <t>{'const': 0.3790909637172042, 'N1ratio-ArgsPreds': -2.7473432321988067, 'Fam_class': -0.00037564029680615127, 'Macro_class': 0.13015781114531866}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 0.0031357338238361095, 'N1ratio-ArgsPreds': 6.948974056809408e-10, 'Fam_class': 0.7910905256429878, 'Macro_class': 9.42111246867944e-06}</t>
+          <t>{'const': 0.0036030532975761973, 'N1ratio-ArgsPreds': 2.7802816721337326e-10, 'Fam_class': 0.7320837246068228, 'Macro_class': 6.412880396547971e-06}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4715640300208119, 'Fam_class': -0.022856974924635984, 'Macro_class': 0.3979397223171519}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47909490725725523, 'Fam_class': -0.02928502948699074, 'Macro_class': 0.4026857335532404}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5296671694897966), 'Fam_class': np.float64(-0.02464417907642201), 'Macro_class': np.float64(0.39529044010156983)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5399979456643251), 'Fam_class': np.float64(-0.03184736040668646), 'Macro_class': np.float64(0.4020070160305793)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4656753652021862), 'Fam_class': np.float64(-0.018383474902530714), 'Macro_class': np.float64(0.32091640171694724)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47475802738123984), 'Fam_class': np.float64(-0.023578379983510613), 'Macro_class': np.float64(0.324885748041981)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.685354575618952), 'Fam_class': np.float64(0.03379521494919766), 'Macro_class': np.float64(10.298733689095306)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.53951845629261), 'Fam_class': np.float64(0.0555940002646814), 'Macro_class': np.float64(10.555074928079756)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.1029873368909565</v>
+        <v>0.1055507492807909</v>
       </c>
       <c r="V4" t="n">
-        <v>21.48221993995741</v>
+        <v>22.36036966090776</v>
       </c>
       <c r="W4" t="n">
-        <v>9.42111246867966e-06</v>
+        <v>6.412880396548521e-06</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4619214611791158</v>
+        <v>0.4641730366459157</v>
       </c>
       <c r="H5" t="n">
-        <v>19.57299642160542</v>
+        <v>19.75105016977905</v>
       </c>
       <c r="I5" t="n">
-        <v>4.924562337235453e-14</v>
+        <v>3.904950328100943e-14</v>
       </c>
       <c r="J5" t="n">
-        <v>13.33986377493442</v>
+        <v>13.28404346648668</v>
       </c>
       <c r="K5" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>2.29036057834645</v>
+        <v>2.301524640035999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1170163489029335</v>
+        <v>0.1165266970744445</v>
       </c>
       <c r="N5" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.17547142028804047, 'N1ratio-ArgsPreds': -2.985367830583771, 'Fam_class': -0.0013547988832419814, 'Macro_class': 0.1203900883589205, 'Nlen_freq': 0.7918523166300431, 'Vlen_freq': -0.05430434078500129}</t>
+          <t>{'const': 0.19847538662574543, 'N1ratio-ArgsPreds': -2.8119941044225776, 'Fam_class': -0.0012336323262051477, 'Macro_class': 0.12455445172273996, 'Nlen_freq': 0.5644678913695289, 'Vlen_freq': 0.0454172635275375}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.318716671773403, 'N1ratio-ArgsPreds': 3.8674299916032e-10, 'Fam_class': 0.27046341802126433, 'Macro_class': 3.3361604837274294e-05, 'Nlen_freq': 0.13000228580547196, 'Vlen_freq': 0.9136473251109498}</t>
+          <t>{'const': 0.25449542530594127, 'N1ratio-ArgsPreds': 3.3058643948219187e-10, 'Fam_class': 0.3140587675905715, 'Macro_class': 1.6779219729329075e-05, 'Nlen_freq': 0.2698047796047915, 'Vlen_freq': 0.9267919252118395}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4916579601658273, 'Fam_class': -0.10562052469348877, 'Macro_class': 0.3724660903311062, 'Nlen_freq': 0.16159289070001537, 'Vlen_freq': -0.01067839295176563}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49036903684875827, 'Fam_class': -0.09617434379694893, 'Macro_class': 0.38534990960546095, 'Nlen_freq': 0.11764332488741631, 'Vlen_freq': 0.009085055355778143}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.540257725193458), 'Fam_class': np.float64(-0.10316169926315122), 'Macro_class': np.float64(0.37514083559807176), 'Nlen_freq': np.float64(0.14140397636960284), 'Vlen_freq': np.float64(-0.010178292349248894)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5420208744613106), 'Fam_class': np.float64(-0.09428630984713471), 'Macro_class': np.float64(0.3880384897849444), 'Nlen_freq': np.float64(0.10330288117195983), 'Vlen_freq': np.float64(0.008624253891634511)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4709446882582684), 'Fam_class': np.float64(-0.07607897649656697), 'Macro_class': np.float64(0.2968605689357376), 'Nlen_freq': np.float64(0.10477805456960126), 'Vlen_freq': np.float64(-0.007466554737971187)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47212861844771997), 'Fam_class': np.float64(-0.06932661118839695), 'Macro_class': np.float64(0.3081940707749217), 'Nlen_freq': np.float64(0.07602465413586444), 'Vlen_freq': np.float64(0.006313206090842647)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.17888993986776), 'Fam_class': np.float64(0.5788010664765191), 'Macro_class': np.float64(8.81261973888498), 'Nlen_freq': np.float64(1.0978440719390339), 'Vlen_freq': np.float64(0.005574943965511998)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.290543235735274), 'Fam_class': np.float64(0.48061790188671644), 'Macro_class': np.float64(9.498358526081747), 'Nlen_freq': np.float64(0.5779748036477811), 'Vlen_freq': np.float64(0.003985657114545269)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.01803396318037043</v>
+        <v>0.01174389984043245</v>
       </c>
       <c r="V5" t="n">
-        <v>1.910382643273</v>
+        <v>1.249288178247753</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1527325792761614</v>
+        <v>0.2906037998719303</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_11_Dunn_lgs_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_11_Dunn_lgs_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2778077214292567</v>
+        <v>0.2755848639634494</v>
       </c>
       <c r="H2" t="n">
-        <v>45.39138966360625</v>
+        <v>44.89002552542782</v>
       </c>
       <c r="I2" t="n">
-        <v>6.23405371411057e-10</v>
+        <v>7.501800790435129e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>17.90435023956635</v>
+        <v>17.95945858090615</v>
       </c>
       <c r="K2" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>6.887316427100323</v>
+        <v>6.832208085760517</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1517317816912402</v>
+        <v>0.152198801533103</v>
       </c>
       <c r="N2" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7491199802103012, 'N1ratio-ArgsPreds': -3.0224806007943616}</t>
+          <t>{'const': 0.7461726021992878, 'N1ratio-ArgsPreds': -3.0029926664449578}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 6.899475278910947e-17, 'N1ratio-ArgsPreds': 6.234053714110714e-10}</t>
+          <t>{'const': 8.338478385942126e-17, 'N1ratio-ArgsPreds': 7.501800790435231e-10}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5270746829712618}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5249617738116265}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5249617738116272)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5249617738116275)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.78077214292572)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(27.558486396345028)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3468783875246924</v>
+        <v>0.3445557602744161</v>
       </c>
       <c r="H3" t="n">
-        <v>31.06984255701949</v>
+        <v>30.75244354041819</v>
       </c>
       <c r="I3" t="n">
-        <v>1.503668952114882e-11</v>
+        <v>1.850723068995827e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>16.19197330928367</v>
+        <v>16.24955510986344</v>
       </c>
       <c r="K3" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2998466786915</v>
+        <v>4.271055778401617</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1383929342673818</v>
+        <v>0.1388850864090892</v>
       </c>
       <c r="N3" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.8694669476332118, 'N1ratio-ArgsPreds': -2.8294009162073523, 'Fam_class': -0.0033986661667828}</t>
+          <t>{'const': 0.8663052721193276, 'N1ratio-ArgsPreds': -2.8090928899172782, 'Fam_class': -0.003396620212338761}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.437321412929333e-19, 'N1ratio-ArgsPreds': 1.606111944602189e-09, 'Fam_class': 0.0006209671097238488}</t>
+          <t>{'const': 4.2574190185320626e-19, 'N1ratio-ArgsPreds': 1.985915714426193e-09, 'Fam_class': 0.0006397822330810478}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49340452028596854, 'Fam_class': -0.2649610272298194}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49106559691947604, 'Fam_class': -0.2648015240116286}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5180004928438996), 'Fam_class': np.float64(-0.30925761460178797)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.51548281300043), 'Fam_class': np.float64(-0.3085596810744864)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48940448749553883), 'Fam_class': np.float64(-0.2628129869230889)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.487025795138713), 'Fam_class': np.float64(-0.26262310696312885)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.9516752380771), 'Fam_class': np.float64(6.907066609543571)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.71941251304957), 'Fam_class': np.float64(6.897089631096702)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.06907066609543566</v>
+        <v>0.06897089631096676</v>
       </c>
       <c r="V3" t="n">
-        <v>12.37329737495327</v>
+        <v>12.3116420578532</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006209671097233587</v>
+        <v>0.0006397822330816575</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4524291368054832</v>
+        <v>0.4506642630178419</v>
       </c>
       <c r="H4" t="n">
-        <v>31.94824231714258</v>
+        <v>31.72137485978972</v>
       </c>
       <c r="I4" t="n">
-        <v>3.96884339424559e-15</v>
+        <v>4.77422020295344e-15</v>
       </c>
       <c r="J4" t="n">
-        <v>13.5751943166974</v>
+        <v>13.61894847934934</v>
       </c>
       <c r="K4" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L4" t="n">
-        <v>3.738824116656425</v>
+        <v>3.724239395772444</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1170275372129086</v>
+        <v>0.1174047282702529</v>
       </c>
       <c r="N4" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.3790909637172042, 'N1ratio-ArgsPreds': -2.7473432321988067, 'Fam_class': -0.00037564029680615127, 'Macro_class': 0.13015781114531866}</t>
+          <t>{'const': 0.37512056148653217, 'N1ratio-ArgsPreds': -2.730007680261724, 'Fam_class': -0.00036513995397773806, 'Macro_class': 0.13049233643816424}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 0.0036030532975761973, 'N1ratio-ArgsPreds': 2.7802816721337326e-10, 'Fam_class': 0.7320837246068228, 'Macro_class': 6.412880396547971e-06}</t>
+          <t>{'const': 0.003969640655783873, 'N1ratio-ArgsPreds': 3.3632666003065007e-10, 'Fam_class': 0.7397301091872172, 'Macro_class': 6.285648886348729e-06}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47909490725725523, 'Fam_class': -0.02928502948699074, 'Macro_class': 0.4026857335532404}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47724048425538385, 'Fam_class': -0.028466419630784928, 'Macro_class': 0.40372069689317575}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5399979456643251), 'Fam_class': np.float64(-0.03184736040668646), 'Macro_class': np.float64(0.4020070160305793)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5378796636228386), 'Fam_class': np.float64(-0.03090415508525273), 'Macro_class': np.float64(0.4023529757543716)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47475802738123984), 'Fam_class': np.float64(-0.023578379983510613), 'Macro_class': np.float64(0.324885748041981)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47289566584531356), 'Fam_class': np.float64(-0.022916236216408228), 'Macro_class': np.float64(0.3257430010658656)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.53951845629261), 'Fam_class': np.float64(0.0555940002646814), 'Macro_class': np.float64(10.555074928079756)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.363031077528248), 'Fam_class': np.float64(0.05251538823262201), 'Macro_class': np.float64(10.610850274339652)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.1055507492807909</v>
+        <v>0.1061085027434258</v>
       </c>
       <c r="V4" t="n">
-        <v>22.36036966090776</v>
+        <v>22.40630909224309</v>
       </c>
       <c r="W4" t="n">
-        <v>6.412880396548521e-06</v>
+        <v>6.285648886348749e-06</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4641730366459157</v>
+        <v>0.4620780808030259</v>
       </c>
       <c r="H5" t="n">
-        <v>19.75105016977905</v>
+        <v>19.5853336075922</v>
       </c>
       <c r="I5" t="n">
-        <v>3.904950328100943e-14</v>
+        <v>4.845893345739595e-14</v>
       </c>
       <c r="J5" t="n">
-        <v>13.28404346648668</v>
+        <v>13.33598091342498</v>
       </c>
       <c r="K5" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>2.301524640035999</v>
+        <v>2.291137150648337</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1165266970744445</v>
+        <v>0.1169822887142543</v>
       </c>
       <c r="N5" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.19847538662574543, 'N1ratio-ArgsPreds': -2.8119941044225776, 'Fam_class': -0.0012336323262051477, 'Macro_class': 0.12455445172273996, 'Nlen_freq': 0.5644678913695289, 'Vlen_freq': 0.0454172635275375}</t>
+          <t>{'const': 0.19756951482543422, 'N1ratio-ArgsPreds': -2.795406722501543, 'Fam_class': -0.0012117068858907081, 'Macro_class': 0.12503015815205834, 'Nlen_freq': 0.5648497079292876, 'Vlen_freq': 0.04252843754089486}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.25449542530594127, 'N1ratio-ArgsPreds': 3.3058643948219187e-10, 'Fam_class': 0.3140587675905715, 'Macro_class': 1.6779219729329075e-05, 'Nlen_freq': 0.2698047796047915, 'Vlen_freq': 0.9267919252118395}</t>
+          <t>{'const': 0.25683082153923337, 'N1ratio-ArgsPreds': 4.1746888508307763e-10, 'Fam_class': 0.32376520854413904, 'Macro_class': 1.6155544701681286e-05, 'Nlen_freq': 0.2772717809095278, 'Vlen_freq': 0.9316641215828176}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49036903684875827, 'Fam_class': -0.09617434379694893, 'Macro_class': 0.38534990960546095, 'Nlen_freq': 0.11764332488741631, 'Vlen_freq': 0.009085055355778143}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48867307868141024, 'Fam_class': -0.09446502993583523, 'Macro_class': 0.38682166293905224, 'Nlen_freq': 0.11640904275939995, 'Vlen_freq': 0.008518109158388864}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5420208744613106), 'Fam_class': np.float64(-0.09428630984713471), 'Macro_class': np.float64(0.3880384897849444), 'Nlen_freq': np.float64(0.10330288117195983), 'Vlen_freq': np.float64(0.008624253891634511)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5393948803658094), 'Fam_class': np.float64(-0.09242206766953988), 'Macro_class': np.float64(0.3887338218876132), 'Nlen_freq': np.float64(0.10171572002683513), 'Vlen_freq': np.float64(0.008048846234252678)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47212861844771997), 'Fam_class': np.float64(-0.06932661118839695), 'Macro_class': np.float64(0.3081940707749217), 'Nlen_freq': np.float64(0.07602465413586444), 'Vlen_freq': np.float64(0.006313206090842647)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4698151760425981), 'Fam_class': np.float64(-0.06807663880811016), 'Macro_class': np.float64(0.3094477000622494), 'Nlen_freq': np.float64(0.07499046134790975), 'Vlen_freq': np.float64(0.005903469439963936)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.290543235735274), 'Fam_class': np.float64(0.48061790188671644), 'Macro_class': np.float64(9.498358526081747), 'Nlen_freq': np.float64(0.5779748036477811), 'Vlen_freq': np.float64(0.003985657114545269)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.07262996399374), 'Fam_class': np.float64(0.463442875140989), 'Macro_class': np.float64(9.575787907381587), 'Nlen_freq': np.float64(0.5623569293172346), 'Vlen_freq': np.float64(0.0034850951428588104)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.01174389984043245</v>
+        <v>0.01141381778518402</v>
       </c>
       <c r="V5" t="n">
-        <v>1.249288178247753</v>
+        <v>1.209446186403235</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2906037998719303</v>
+        <v>0.3021615041985532</v>
       </c>
     </row>
   </sheetData>
